--- a/CCSJV_Drawing_Register.xlsx
+++ b/CCSJV_Drawing_Register.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>066-IA-0074_512_0.pdf</t>
+          <t>033-AV-0026_512_0.pdf</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -514,22 +514,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>066-IA-0074/512</t>
+          <t>033-AV-0026/512</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MZ-066-CCX-PI-ISO-IA0074-512</t>
+          <t>MZ-033-CCX-PI-ISO-AV0026-512</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>066-1"-IA-0074-01SA0S01-P</t>
+          <t>033-2"-AV-0026-01CB1S01-P</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MZ-066-CCX-PR-PID-00200-01</t>
+          <t>MZ-033-CCX-PR-PID-00009-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -539,455 +539,50 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>01CB1S01</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>VISUAL</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>01SA0S01</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>066-IA-0074_512_0.pdf</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>066-IA-0074/512</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PI-ISO-IA0074-512</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>066-1"-IA-0074-01SA0S01-P</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PR-PID-00200-01</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>01SA0S01</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>066-PA-0012_512_1.pdf</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>066-PA-0012/512</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PI-ISO-PA0012-512</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>066-2"-PA-0012-01CG1T01-P</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PR-PID-00201-01</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>01CG1T01</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>066-PA-0012_512_1.pdf</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>066-PA-0012/512</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PI-ISO-PA0012-512</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>066-2"-PA-0012-01CG1T01-P</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PR-PID-00201-01</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>01CG1T01</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>066-PA-0012_512_1.pdf</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>066-PA-0012/512</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PI-ISO-PA0012-512</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>066-2"-PA-0012-01CG1T01-P</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PR-PID-00201-01</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>01CG1T01</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>066-PA-0012_512_1.pdf</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>066-PA-0012/512</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PI-ISO-PA0012-512</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>066-2"-PA-0012-01CG1T01-P</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>MZ-066-CCX-PR-PID-00201-01</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>01CG1T01</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>SERVICE</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CCSJV_Drawing_Register.xlsx
+++ b/CCSJV_Drawing_Register.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>033-AV-0026_512_0.pdf</t>
+          <t>076-FW-0028_512_0.pdf</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -514,24 +514,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>033-AV-0026/512</t>
+          <t>076-FW-0028/512</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MZ-033-CCX-PI-ISO-AV0026-512</t>
+          <t>MZ-076-CCX-PI-ISO-FW0028-512</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>033-2"-AV-0026-01CB1S01-P</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>MZ-033-CCX-PR-PID-00009-01</t>
-        </is>
-      </c>
+          <t>076-4"-FW-0028-01CB2S70-P</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>0</t>
@@ -539,12 +535,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>01CB1S01</t>
+          <t>01CB2S70</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -569,20 +565,97 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>VISUAL</t>
+          <t>HYDRO</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>076-FW-0028_512_0.pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>076-FW-0083/512</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MZ-076-CCX-PI-ISO-FW0028-512</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>076-4"-FW-0028-01CB2S70-P</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>01CB2S70</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>16.00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>HYDRO</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CCSJV_Drawing_Register.xlsx
+++ b/CCSJV_Drawing_Register.xlsx
@@ -506,155 +506,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>076-FW-0028_512_0.pdf</t>
+          <t>033-PG-0025_512_0.pdf</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>076-FW-0028/512</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MZ-076-CCX-PI-ISO-FW0028-512</t>
+          <t>MZ-033-CCX-PI-ISO-PG0025-512</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>076-4"-FW-0028-01CB2S70-P</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>033-2"-PG-0025-01CB1S01-P</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MZ-033-CCX-PR-PID-00009-01</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>01CB2S70</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>32.00</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>16.00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>HYDRO</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>076-FW-0028_512_0.pdf</t>
+          <t>033-PG-0025_512_0.pdf</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>076-FW-0083/512</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MZ-076-CCX-PI-ISO-FW0028-512</t>
+          <t>MZ-033-CCX-PI-ISO-PG0025-512</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>076-4"-FW-0028-01CB2S70-P</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>033-2"-PG-0025-01CB1S01-P</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MZ-033-CCX-PR-PID-00009-01</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>01CB2S70</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>32.00</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>16.00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>HYDRO</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
     </row>
   </sheetData>
